--- a/backtest_runs/20260410_193731/by_symbol/DADX/DADX.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DADX/DADX.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-3285.959999999998</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>96714.04000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>98982.52</v>
@@ -863,7 +863,7 @@
         <v>-5220.839999999993</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>111976.24</v>
@@ -909,7 +909,7 @@
         <v>-6471.840000000005</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>105504.4</v>
@@ -1093,7 +1093,7 @@
         <v>-9907.920000000007</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>108673.6</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>108673.6</v>
@@ -1231,7 +1231,7 @@
         <v>-6455.160000000007</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>106271.68</v>
@@ -1369,7 +1369,7 @@
         <v>-2768.879999999994</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>103502.8</v>
@@ -1415,7 +1415,7 @@
         <v>-4970.639999999995</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>98532.15999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-116.7600000000005</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>98415.39999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-2919</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>98448.75999999998</v>
